--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J743"/>
+  <dimension ref="A1:J747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27188,6 +27188,150 @@
         <v>371</v>
       </c>
       <c r="J743" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>308.29</v>
+      </c>
+      <c r="C744" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="D744" t="n">
+        <v>365.58</v>
+      </c>
+      <c r="E744" t="n">
+        <v>377.72</v>
+      </c>
+      <c r="F744" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="G744" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="H744" t="n">
+        <v>370.32</v>
+      </c>
+      <c r="I744" t="n">
+        <v>369.22</v>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>292.62</v>
+      </c>
+      <c r="C745" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="D745" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="E745" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="F745" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="G745" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="H745" t="n">
+        <v>370.46</v>
+      </c>
+      <c r="I745" t="n">
+        <v>369.76</v>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="C746" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="D746" t="n">
+        <v>364.61</v>
+      </c>
+      <c r="E746" t="n">
+        <v>376.74</v>
+      </c>
+      <c r="F746" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="G746" t="n">
+        <v>377.17</v>
+      </c>
+      <c r="H746" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="I746" t="n">
+        <v>369.89</v>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="C747" t="n">
+        <v>360</v>
+      </c>
+      <c r="D747" t="n">
+        <v>364.04</v>
+      </c>
+      <c r="E747" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="F747" t="n">
+        <v>373.62</v>
+      </c>
+      <c r="G747" t="n">
+        <v>377.4</v>
+      </c>
+      <c r="H747" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="I747" t="n">
+        <v>370</v>
+      </c>
+      <c r="J747" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27204,7 +27348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B754"/>
+  <dimension ref="A1:B758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34747,6 +34891,46 @@
       </c>
       <c r="B754" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -34915,28 +35099,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2802732379924048</v>
+        <v>0.2311784413870999</v>
       </c>
       <c r="J2" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K2" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003415405560103446</v>
+        <v>0.002336341930362029</v>
       </c>
       <c r="M2" t="n">
-        <v>30.90797373987396</v>
+        <v>30.9871360613653</v>
       </c>
       <c r="N2" t="n">
-        <v>1244.460972768022</v>
+        <v>1248.445041515977</v>
       </c>
       <c r="O2" t="n">
-        <v>35.27691841371667</v>
+        <v>35.33334178245778</v>
       </c>
       <c r="P2" t="n">
-        <v>328.5027858621497</v>
+        <v>329.0296264322225</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34993,28 +35177,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8810230231722864</v>
+        <v>0.8804594310390875</v>
       </c>
       <c r="J3" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K3" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4768642889760455</v>
+        <v>0.4797636448733279</v>
       </c>
       <c r="M3" t="n">
-        <v>5.513292279811623</v>
+        <v>5.486112830517341</v>
       </c>
       <c r="N3" t="n">
-        <v>46.23173726873362</v>
+        <v>45.98530586048953</v>
       </c>
       <c r="O3" t="n">
-        <v>6.799392419086695</v>
+        <v>6.781246630265672</v>
       </c>
       <c r="P3" t="n">
-        <v>336.6020875250856</v>
+        <v>336.6081341028866</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35071,28 +35255,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.009600033670012</v>
+        <v>1.005830084194235</v>
       </c>
       <c r="J4" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K4" t="n">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6257631031135645</v>
+        <v>0.6266099982058757</v>
       </c>
       <c r="M4" t="n">
-        <v>4.517445033578371</v>
+        <v>4.508658177384811</v>
       </c>
       <c r="N4" t="n">
-        <v>32.94424808569447</v>
+        <v>32.82838406925998</v>
       </c>
       <c r="O4" t="n">
-        <v>5.73970801397549</v>
+        <v>5.729605926175026</v>
       </c>
       <c r="P4" t="n">
-        <v>340.9171137811949</v>
+        <v>340.9576970113141</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35149,28 +35333,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.079247599005792</v>
+        <v>1.073355734743986</v>
       </c>
       <c r="J5" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K5" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6813907676721154</v>
+        <v>0.6807392190755411</v>
       </c>
       <c r="M5" t="n">
-        <v>4.354980659628102</v>
+        <v>4.355661362205154</v>
       </c>
       <c r="N5" t="n">
-        <v>29.56993873531879</v>
+        <v>29.5582813341623</v>
       </c>
       <c r="O5" t="n">
-        <v>5.437824816534529</v>
+        <v>5.436752829967746</v>
       </c>
       <c r="P5" t="n">
-        <v>353.1972685264525</v>
+        <v>353.2604900503999</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35227,28 +35411,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8395877193717232</v>
+        <v>0.8359062203609017</v>
       </c>
       <c r="J6" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K6" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5846372873091719</v>
+        <v>0.58512896720259</v>
       </c>
       <c r="M6" t="n">
-        <v>4.129448789294147</v>
+        <v>4.12390817180971</v>
       </c>
       <c r="N6" t="n">
-        <v>27.1906307881008</v>
+        <v>27.10214377150982</v>
       </c>
       <c r="O6" t="n">
-        <v>5.214463614610884</v>
+        <v>5.205971933415491</v>
       </c>
       <c r="P6" t="n">
-        <v>354.3139123050634</v>
+        <v>354.3534154107854</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35305,28 +35489,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4215265564228082</v>
+        <v>0.4236837720560654</v>
       </c>
       <c r="J7" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K7" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2773558986267</v>
+        <v>0.2818587181173583</v>
       </c>
       <c r="M7" t="n">
-        <v>3.833479956141614</v>
+        <v>3.821941014477435</v>
       </c>
       <c r="N7" t="n">
-        <v>25.13524182284901</v>
+        <v>25.02010321760878</v>
       </c>
       <c r="O7" t="n">
-        <v>5.013505941240023</v>
+        <v>5.002009917783929</v>
       </c>
       <c r="P7" t="n">
-        <v>363.9341786142181</v>
+        <v>363.9110311994275</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35383,28 +35567,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3461278074085686</v>
+        <v>0.3519180994113937</v>
       </c>
       <c r="J8" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K8" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2196545596242397</v>
+        <v>0.2265864207005173</v>
       </c>
       <c r="M8" t="n">
-        <v>3.731070335446856</v>
+        <v>3.738462243405229</v>
       </c>
       <c r="N8" t="n">
-        <v>23.10818245674959</v>
+        <v>23.12534059403535</v>
       </c>
       <c r="O8" t="n">
-        <v>4.807097092502874</v>
+        <v>4.808881428568951</v>
       </c>
       <c r="P8" t="n">
-        <v>355.8550551889519</v>
+        <v>355.7929266742443</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35461,28 +35645,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5663102967862139</v>
+        <v>0.5739469271038109</v>
       </c>
       <c r="J9" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K9" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4616922012840036</v>
+        <v>0.4685666725029143</v>
       </c>
       <c r="M9" t="n">
-        <v>3.536744462234814</v>
+        <v>3.553941232466176</v>
       </c>
       <c r="N9" t="n">
-        <v>20.30173620740921</v>
+        <v>20.43844628886008</v>
       </c>
       <c r="O9" t="n">
-        <v>4.505744800519578</v>
+        <v>4.520889988581903</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6382601122133</v>
+        <v>347.5563182530685</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35520,7 +35704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J743"/>
+  <dimension ref="A1:J747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74155,6 +74339,214 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>-39.84074860218754,176.9978983241548</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>-39.84154389171855,176.9976430897525</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>-39.8420411805751,176.99702268979425</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>-39.84256155383441,176.99650335893364</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>-39.84312402252707,176.99606091903775</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>-39.84372446695199,176.99567714563355</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>-39.84434253357515,176.99534922637017</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>-39.84500531494775,176.99511437863532</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>-39.84064650099201,176.99777220727705</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>-39.841543565933314,176.997642687332</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>-39.842036300384954,176.9970164766756</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-39.8425571624768,176.99649537975088</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>-39.84312165979578,176.99605475253875</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>-39.843725073567995,176.99567921893555</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>-39.84434283577908,176.9953508126991</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>-39.84500637912651,176.99512052842937</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>-39.84058994455047,176.99770234818556</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>-39.841545781272885,176.99764542379162</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>-39.842034951911295,176.99701475989298</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>-39.842556430583805,176.9964940498872</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>-39.843121579703194,176.9960545435049</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>-39.84372485007789,176.99567845508744</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>-39.84434296529504,176.99535149255433</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>-39.845006635317645,176.99512200893537</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>-39.84058994455047,176.99770234818556</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>-39.84154584642993,176.99764550427574</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>-39.84203129176835,176.99701010005472</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>-39.84255616919345,176.99649357493587</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>-39.8431223005365,176.99605642480964</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>-39.84372558440249,176.99568096487408</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>-39.8443421018552,176.995346960186</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>-39.84500685209474,176.9951232616712</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J747"/>
+  <dimension ref="A1:J752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27308,7 +27308,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>283.94</v>
+        <v>286.95</v>
       </c>
       <c r="C747" t="n">
         <v>360</v>
@@ -27332,6 +27332,186 @@
         <v>370</v>
       </c>
       <c r="J747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>289.58</v>
+      </c>
+      <c r="C748" t="n">
+        <v>359.87</v>
+      </c>
+      <c r="D748" t="n">
+        <v>363.95</v>
+      </c>
+      <c r="E748" t="n">
+        <v>376.8</v>
+      </c>
+      <c r="F748" t="n">
+        <v>374.17</v>
+      </c>
+      <c r="G748" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="H748" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="I748" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>292.36</v>
+      </c>
+      <c r="C749" t="n">
+        <v>359.27</v>
+      </c>
+      <c r="D749" t="n">
+        <v>363.18</v>
+      </c>
+      <c r="E749" t="n">
+        <v>376.16</v>
+      </c>
+      <c r="F749" t="n">
+        <v>373.64</v>
+      </c>
+      <c r="G749" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="H749" t="n">
+        <v>369.72</v>
+      </c>
+      <c r="I749" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>295.39</v>
+      </c>
+      <c r="C750" t="n">
+        <v>358.87</v>
+      </c>
+      <c r="D750" t="n">
+        <v>362.78</v>
+      </c>
+      <c r="E750" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="F750" t="n">
+        <v>373.88</v>
+      </c>
+      <c r="G750" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="H750" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="I750" t="n">
+        <v>369.64</v>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:27+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>297.94</v>
+      </c>
+      <c r="C751" t="n">
+        <v>358.17</v>
+      </c>
+      <c r="D751" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="E751" t="n">
+        <v>375.06</v>
+      </c>
+      <c r="F751" t="n">
+        <v>373.66</v>
+      </c>
+      <c r="G751" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="H751" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="I751" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>296.77</v>
+      </c>
+      <c r="C752" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="D752" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="E752" t="n">
+        <v>374.94</v>
+      </c>
+      <c r="F752" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="G752" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="H752" t="n">
+        <v>369.75</v>
+      </c>
+      <c r="I752" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="J752" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27348,7 +27528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B758"/>
+  <dimension ref="A1:B763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34931,6 +35111,56 @@
       </c>
       <c r="B758" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -35099,28 +35329,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2311784413870999</v>
+        <v>0.175847303375026</v>
       </c>
       <c r="J2" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K2" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002336341930362029</v>
+        <v>0.001363221276614257</v>
       </c>
       <c r="M2" t="n">
-        <v>30.9871360613653</v>
+        <v>31.05650507643186</v>
       </c>
       <c r="N2" t="n">
-        <v>1248.445041515977</v>
+        <v>1250.670635498519</v>
       </c>
       <c r="O2" t="n">
-        <v>35.33334178245778</v>
+        <v>35.36482200575197</v>
       </c>
       <c r="P2" t="n">
-        <v>329.0296264322225</v>
+        <v>329.6246057973317</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35177,28 +35407,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8804594310390875</v>
+        <v>0.8782965221838653</v>
       </c>
       <c r="J3" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K3" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4797636448733279</v>
+        <v>0.4823956181740949</v>
       </c>
       <c r="M3" t="n">
-        <v>5.486112830517341</v>
+        <v>5.458603420779082</v>
       </c>
       <c r="N3" t="n">
-        <v>45.98530586048953</v>
+        <v>45.69905746084422</v>
       </c>
       <c r="O3" t="n">
-        <v>6.781246630265672</v>
+        <v>6.760107799498779</v>
       </c>
       <c r="P3" t="n">
-        <v>336.6081341028866</v>
+        <v>336.631404851851</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35255,28 +35485,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.005830084194235</v>
+        <v>0.9986377488892252</v>
       </c>
       <c r="J4" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K4" t="n">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6266099982058757</v>
+        <v>0.6256938935392784</v>
       </c>
       <c r="M4" t="n">
-        <v>4.508658177384811</v>
+        <v>4.508237977906433</v>
       </c>
       <c r="N4" t="n">
-        <v>32.82838406925998</v>
+        <v>32.78920977383199</v>
       </c>
       <c r="O4" t="n">
-        <v>5.729605926175026</v>
+        <v>5.726186320216274</v>
       </c>
       <c r="P4" t="n">
-        <v>340.9576970113141</v>
+        <v>341.0352937749424</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35333,28 +35563,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.073355734743986</v>
+        <v>1.064411525847585</v>
       </c>
       <c r="J5" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K5" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6807392190755411</v>
+        <v>0.6784980254264431</v>
       </c>
       <c r="M5" t="n">
-        <v>4.355661362205154</v>
+        <v>4.363415179006948</v>
       </c>
       <c r="N5" t="n">
-        <v>29.5582813341623</v>
+        <v>29.64043141215519</v>
       </c>
       <c r="O5" t="n">
-        <v>5.436752829967746</v>
+        <v>5.444302656186116</v>
       </c>
       <c r="P5" t="n">
-        <v>353.2604900503999</v>
+        <v>353.3566825223505</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35411,28 +35641,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8359062203609017</v>
+        <v>0.8316866667494019</v>
       </c>
       <c r="J6" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K6" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L6" t="n">
-        <v>0.58512896720259</v>
+        <v>0.5859762352695939</v>
       </c>
       <c r="M6" t="n">
-        <v>4.12390817180971</v>
+        <v>4.115400706744873</v>
       </c>
       <c r="N6" t="n">
-        <v>27.10214377150982</v>
+        <v>26.98330062041012</v>
       </c>
       <c r="O6" t="n">
-        <v>5.205971933415491</v>
+        <v>5.194545275614615</v>
       </c>
       <c r="P6" t="n">
-        <v>354.3534154107854</v>
+        <v>354.3987916590719</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35489,28 +35719,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4236837720560654</v>
+        <v>0.4262375287003884</v>
       </c>
       <c r="J7" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K7" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2818587181173583</v>
+        <v>0.2873517459921221</v>
       </c>
       <c r="M7" t="n">
-        <v>3.821941014477435</v>
+        <v>3.807089055181827</v>
       </c>
       <c r="N7" t="n">
-        <v>25.02010321760878</v>
+        <v>24.87683251117408</v>
       </c>
       <c r="O7" t="n">
-        <v>5.002009917783929</v>
+        <v>4.987668043402055</v>
       </c>
       <c r="P7" t="n">
-        <v>363.9110311994275</v>
+        <v>363.8835741237715</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35567,28 +35797,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3519180994113937</v>
+        <v>0.3580056855356687</v>
       </c>
       <c r="J8" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K8" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2265864207005173</v>
+        <v>0.2345042508925049</v>
       </c>
       <c r="M8" t="n">
-        <v>3.738462243405229</v>
+        <v>3.742372387477229</v>
       </c>
       <c r="N8" t="n">
-        <v>23.12534059403535</v>
+        <v>23.0994818393688</v>
       </c>
       <c r="O8" t="n">
-        <v>4.808881428568951</v>
+        <v>4.80619203105419</v>
       </c>
       <c r="P8" t="n">
-        <v>355.7929266742443</v>
+        <v>355.7274653388217</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35645,28 +35875,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5739469271038109</v>
+        <v>0.5830383432329016</v>
       </c>
       <c r="J9" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K9" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4685666725029143</v>
+        <v>0.4768852958861088</v>
       </c>
       <c r="M9" t="n">
-        <v>3.553941232466176</v>
+        <v>3.573851873758856</v>
       </c>
       <c r="N9" t="n">
-        <v>20.43844628886008</v>
+        <v>20.58768697515665</v>
       </c>
       <c r="O9" t="n">
-        <v>4.520889988581903</v>
+        <v>4.537365642656171</v>
       </c>
       <c r="P9" t="n">
-        <v>347.5563182530685</v>
+        <v>347.4585576171825</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35704,7 +35934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J747"/>
+  <dimension ref="A1:J752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74503,7 +74733,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>-39.84058994455047,176.99770234818556</t>
+          <t>-39.840609556870334,176.9977265735026</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -74542,6 +74772,266 @@
         </is>
       </c>
       <c r="J747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>-39.840626693211505,176.99774774048535</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>-39.84154499938835,176.99764445798232</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>-39.84203071385103,176.99700936429082</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>-39.84255674425225,176.99649461982878</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>-39.843124503082535,176.99606217324097</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>-39.84372663799857,176.9956845658724</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>-39.84434218819919,176.99534741342282</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>-39.84500697033678,176.99512394498169</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>-39.84064480690575,176.99777011472196</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>-39.84154108996547,176.99763962893616</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>-39.84202576944702,176.99700306942253</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>-39.842553398455514,176.9964885404522</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>-39.8431223806291,176.9960566338435</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>-39.84372542476672,176.9956804192683</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>-39.844341238415176,176.99534242781777</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>-39.84500649736858,176.99512121173984</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>-39.840664549523666,176.99779450104367</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>-39.84153848368344,176.99763640957235</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>-39.842023200925304,176.99699979936142</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>-39.842550941385824,176.99648407591036</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>-39.843123341740124,176.99605914224983</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>-39.84372523320378,176.99567976454134</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>-39.844340785109075,176.9953400483245</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>-39.84500614264236,176.99511916180845</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:27+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>-39.84068116459358,176.9978150241966</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>-39.84153392268963,176.99763077568628</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>-39.84202011869912,176.99699587528843</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>-39.84254764786659,176.996478091525</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>-39.843122460721695,176.99605684287735</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>-39.84372357299148,176.9956740902412</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>-39.844340698765045,176.99533959508767</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>-39.845005768209106,176.99511699799203</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>-39.84067354120908,176.9978056076899</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>-39.84153177250672,176.99762811971166</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>-39.842020054486056,176.99699579353694</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-39.842547020529565,176.99647695164217</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-39.8431234218327,176.99605935128372</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>-39.84372398804458,176.99567550881622</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>-39.84434130317319,176.99534276774537</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>-39.845005571138955,176.9951158591413</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0297/nzd0297.xlsx
+++ b/data/nzd0297/nzd0297.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J752"/>
+  <dimension ref="A1:J757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27512,6 +27512,186 @@
         <v>369.35</v>
       </c>
       <c r="J752" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>299.38</v>
+      </c>
+      <c r="C753" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="D753" t="n">
+        <v>362.13</v>
+      </c>
+      <c r="E753" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="F753" t="n">
+        <v>373.96</v>
+      </c>
+      <c r="G753" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="H753" t="n">
+        <v>369.06</v>
+      </c>
+      <c r="I753" t="n">
+        <v>368.68</v>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>301.83</v>
+      </c>
+      <c r="C754" t="n">
+        <v>356.59</v>
+      </c>
+      <c r="D754" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="E754" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="F754" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="G754" t="n">
+        <v>376.37</v>
+      </c>
+      <c r="H754" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="I754" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>303.95</v>
+      </c>
+      <c r="C755" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="D755" t="n">
+        <v>361.69</v>
+      </c>
+      <c r="E755" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="F755" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="G755" t="n">
+        <v>376.15</v>
+      </c>
+      <c r="H755" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="I755" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>303.9</v>
+      </c>
+      <c r="C756" t="n">
+        <v>355.98</v>
+      </c>
+      <c r="D756" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="E756" t="n">
+        <v>375.08</v>
+      </c>
+      <c r="F756" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="G756" t="n">
+        <v>376.41</v>
+      </c>
+      <c r="H756" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="I756" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>306.14</v>
+      </c>
+      <c r="C757" t="n">
+        <v>355.91</v>
+      </c>
+      <c r="D757" t="n">
+        <v>361.83</v>
+      </c>
+      <c r="E757" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="F757" t="n">
+        <v>373.95</v>
+      </c>
+      <c r="G757" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="H757" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="I757" t="n">
+        <v>366.82</v>
+      </c>
+      <c r="J757" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27528,7 +27708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B763"/>
+  <dimension ref="A1:B768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35161,6 +35341,56 @@
       </c>
       <c r="B763" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -35329,28 +35559,28 @@
         <v>0.054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.175847303375026</v>
+        <v>0.1333433232909199</v>
       </c>
       <c r="J2" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K2" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001363221276614257</v>
+        <v>0.0007926521677174003</v>
       </c>
       <c r="M2" t="n">
-        <v>31.05650507643186</v>
+        <v>31.06027429305152</v>
       </c>
       <c r="N2" t="n">
-        <v>1250.670635498519</v>
+        <v>1248.789672904073</v>
       </c>
       <c r="O2" t="n">
-        <v>35.36482200575197</v>
+        <v>35.33821830404121</v>
       </c>
       <c r="P2" t="n">
-        <v>329.6246057973317</v>
+        <v>330.0834471549083</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35407,28 +35637,28 @@
         <v>0.0601</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8782965221838653</v>
+        <v>0.8728404714242997</v>
       </c>
       <c r="J3" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K3" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4823956181740949</v>
+        <v>0.4826227451153864</v>
       </c>
       <c r="M3" t="n">
-        <v>5.458603420779082</v>
+        <v>5.444905851941877</v>
       </c>
       <c r="N3" t="n">
-        <v>45.69905746084422</v>
+        <v>45.50331937534494</v>
       </c>
       <c r="O3" t="n">
-        <v>6.760107799498779</v>
+        <v>6.74561482559929</v>
       </c>
       <c r="P3" t="n">
-        <v>336.631404851851</v>
+        <v>336.6903148519215</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35485,28 +35715,28 @@
         <v>0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9986377488892252</v>
+        <v>0.9901131628623153</v>
       </c>
       <c r="J4" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K4" t="n">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6256938935392784</v>
+        <v>0.6235448456062576</v>
       </c>
       <c r="M4" t="n">
-        <v>4.508237977906433</v>
+        <v>4.513318502398314</v>
       </c>
       <c r="N4" t="n">
-        <v>32.78920977383199</v>
+        <v>32.82616807272755</v>
       </c>
       <c r="O4" t="n">
-        <v>5.726186320216274</v>
+        <v>5.729412541677162</v>
       </c>
       <c r="P4" t="n">
-        <v>341.0352937749424</v>
+        <v>341.1276150227246</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35563,28 +35793,28 @@
         <v>0.0574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.064411525847585</v>
+        <v>1.054442791632145</v>
       </c>
       <c r="J5" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K5" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6784980254264431</v>
+        <v>0.6752359960219395</v>
       </c>
       <c r="M5" t="n">
-        <v>4.363415179006948</v>
+        <v>4.376317778990159</v>
       </c>
       <c r="N5" t="n">
-        <v>29.64043141215519</v>
+        <v>29.79422734635753</v>
       </c>
       <c r="O5" t="n">
-        <v>5.444302656186116</v>
+        <v>5.458408865810395</v>
       </c>
       <c r="P5" t="n">
-        <v>353.3566825223505</v>
+        <v>353.4643030210938</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35641,28 +35871,28 @@
         <v>0.0553</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8316866667494019</v>
+        <v>0.8276570172609095</v>
       </c>
       <c r="J6" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K6" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5859762352695939</v>
+        <v>0.5869146595488541</v>
       </c>
       <c r="M6" t="n">
-        <v>4.115400706744873</v>
+        <v>4.106224862665836</v>
       </c>
       <c r="N6" t="n">
-        <v>26.98330062041012</v>
+        <v>26.86206592827012</v>
       </c>
       <c r="O6" t="n">
-        <v>5.194545275614615</v>
+        <v>5.182862715553068</v>
       </c>
       <c r="P6" t="n">
-        <v>354.3987916590719</v>
+        <v>354.4422949836226</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35719,28 +35949,28 @@
         <v>0.0554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4262375287003884</v>
+        <v>0.4275444078978626</v>
       </c>
       <c r="J7" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K7" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2873517459921221</v>
+        <v>0.2917907665590898</v>
       </c>
       <c r="M7" t="n">
-        <v>3.807089055181827</v>
+        <v>3.787286063971564</v>
       </c>
       <c r="N7" t="n">
-        <v>24.87683251117408</v>
+        <v>24.71873731167115</v>
       </c>
       <c r="O7" t="n">
-        <v>4.987668043402055</v>
+        <v>4.971794174306812</v>
       </c>
       <c r="P7" t="n">
-        <v>363.8835741237715</v>
+        <v>363.8694673832352</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35797,28 +36027,28 @@
         <v>0.0484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3580056855356687</v>
+        <v>0.3619255128492432</v>
       </c>
       <c r="J8" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K8" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2345042508925049</v>
+        <v>0.2408610064224465</v>
       </c>
       <c r="M8" t="n">
-        <v>3.742372387477229</v>
+        <v>3.736052697894092</v>
       </c>
       <c r="N8" t="n">
-        <v>23.0994818393688</v>
+        <v>23.00207322719554</v>
       </c>
       <c r="O8" t="n">
-        <v>4.80619203105419</v>
+        <v>4.79604766731895</v>
       </c>
       <c r="P8" t="n">
-        <v>355.7274653388217</v>
+        <v>355.6851527116374</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35875,28 +36105,28 @@
         <v>0.0611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5830383432329016</v>
+        <v>0.5890638241057249</v>
       </c>
       <c r="J9" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="K9" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4768852958861088</v>
+        <v>0.4843491113852549</v>
       </c>
       <c r="M9" t="n">
-        <v>3.573851873758856</v>
+        <v>3.579322715632254</v>
       </c>
       <c r="N9" t="n">
-        <v>20.58768697515665</v>
+        <v>20.5823874742781</v>
       </c>
       <c r="O9" t="n">
-        <v>4.537365642656171</v>
+        <v>4.536781620739322</v>
       </c>
       <c r="P9" t="n">
-        <v>347.4585576171825</v>
+        <v>347.3935162567649</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35934,7 +36164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J752"/>
+  <dimension ref="A1:J757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75037,6 +75267,266 @@
         </is>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>-39.84069054721945,176.99782661374618</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>-39.84152831918252,176.99762385405583</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>-39.8420190270773,176.99699448551266</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-39.84254665458295,176.9964762867105</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>-39.843123662110436,176.99605997838535</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>-39.84372382840878,176.99567496321046</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>-39.844339813738706,176.9953349494104</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>-39.84500425076866,176.99510822884145</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>-39.84070651071185,176.99784633208438</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>-39.841523627873876,176.99761805920332</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>-39.842015623785635,176.99699015268263</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>-39.84254440662511,176.99647220213046</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>-39.843123021369784,176.99605830611438</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>-39.8437222959049,176.99566972539515</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>-39.844338648093974,176.99532883071365</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>-39.845003304831394,176.99510276235813</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>-39.8407203240164,176.99786339449054</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>-39.841521412533574,176.99761532274545</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>-39.8420162017031,176.9969908884462</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-39.84254675913912,176.99647647669096</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>-39.843123381786405,176.9960592467668</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>-39.843721593507205,176.99566732472985</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>-39.84433778465321,176.99532429834582</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>-39.84500204358128,176.9950954737139</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>-39.840719998230945,176.9978629920752</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>-39.84151965329268,176.9976131496761</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>-39.84201767860326,176.9969927687309</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>-39.84254775242276,176.9964782815055</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>-39.84312466326769,176.99606259130871</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>-39.84372242361358,176.99567016187973</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>-39.84433774148116,176.99532407172742</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>-39.84500141295608,176.9950918293919</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>-39.84073459341763,176.99788102028523</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>-39.84151919719319,176.99761258628777</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>-39.84201710068581,176.9969920329673</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>-39.84254707280765,176.9964770466324</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>-39.843123622064155,176.99605987386838</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>-39.84372175314304,176.9956678703356</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>-39.84433709390045,176.9953206724516</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>-39.845000585260294,176.99508704621934</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
